--- a/www/download/COUNTRY.MEX.rpA2.xlsx
+++ b/www/download/COUNTRY.MEX.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>México</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>6.35849179152629</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>7.59647510320646</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>7.91577600833963</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>9.08265203935181</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>9.55018640900463</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>9.45268957486545</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>9.33706799371899</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>9.63669632390332</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>10.7805091591203</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>11.2828615564097</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>10.8932465571719</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>10.8944331590875</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>10.927767684041</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>11.0314278268707</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>13.4917259917644</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>33.128</t>
+          <t>5.55760909910227</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>34.307</t>
+          <t>5.93478503671184</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>35.189</t>
+          <t>6.15848426676041</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>36.555</t>
+          <t>5.56708671389403</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>37.969</t>
+          <t>5.23375988051232</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>39.226</t>
+          <t>5.06665548476875</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>40.103</t>
+          <t>4.50176808871756</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>40.958</t>
+          <t>4.51722951447199</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>41.656</t>
+          <t>4.50866277926277</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>43.032</t>
+          <t>4.66526391599498</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>43.702</t>
+          <t>5.28350217036866</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>45.269</t>
+          <t>5.27903875554174</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>5.44841577874721</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>49.694</t>
+          <t>5.66762665671029</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>49.056</t>
+          <t>5.68669322245863</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20.399</t>
+          <t>3.09142495557962</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21.259</t>
+          <t>3.25946427618487</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>3.48509010209012</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23.215</t>
+          <t>3.24192219549142</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>24.044</t>
+          <t>3.09713478229418</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>24.921</t>
+          <t>3.00633267105245</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>25.354</t>
+          <t>2.63534310389329</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>25.781</t>
+          <t>2.65861170464332</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>26.229</t>
+          <t>2.75401625158</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>2.91767286855795</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>27.858</t>
+          <t>2.84346874059985</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>28.869</t>
+          <t>3.11710988159305</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>3.23952692852552</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>31.816</t>
+          <t>3.32104246638399</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>31.359</t>
+          <t>3.35768961471732</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>72200.833</t>
+          <t>3.65512658803481</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>74795.877</t>
+          <t>4.04518799238326</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>76346.732</t>
+          <t>4.16988375460694</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>78831.744</t>
+          <t>3.92012788838565</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>82030.457</t>
+          <t>3.70459914763541</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>84949.798</t>
+          <t>3.56367005567233</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>86514.939</t>
+          <t>3.17240846436263</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>88013.122</t>
+          <t>3.22811199280807</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>90547.766</t>
+          <t>3.38898298101295</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>94579.114</t>
+          <t>3.47404053431013</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>95650.793</t>
+          <t>3.28610324381912</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>98012.058</t>
+          <t>3.66069957445414</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>99244.457</t>
+          <t>3.86150334623233</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>106428.421</t>
+          <t>4.20608148663244</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>104819.379</t>
+          <t>4.21696780486383</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>44931.874</t>
+          <t>138280817570.819</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>46891.213</t>
+          <t>146026581321.449</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>49276.104</t>
+          <t>148962435578.357</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>50654.784</t>
+          <t>157876082685.875</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>52599.157</t>
+          <t>164495210914.768</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>54687.85</t>
+          <t>171969210624.461</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>55434.331</t>
+          <t>177649907304.53</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>56193.202</t>
+          <t>176837960802.21</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>57784.359</t>
+          <t>179847025355.162</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>60451.696</t>
+          <t>190861466416.876</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>61776.779</t>
+          <t>200438239376.644</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>63475.481</t>
+          <t>200216123175.096</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>64351.89</t>
+          <t>199076003219.907</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>69062.343</t>
+          <t>212477195468.931</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>67913.887</t>
+          <t>205295281209.604</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>21200904389.4558</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>21078134725.5264</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>21702584352.1246</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>25.87</t>
+          <t>23641185935.2962</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25.82</t>
+          <t>25609662008.4698</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>27374635843.0491</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>31115137776.5372</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>31598410176.233</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>31912838510.7992</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>32688118378.0246</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>33508797856.9039</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>32864276816.6835</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>32400703940.696</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>33701914986.1262</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>33025713807.0334</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>50.18</t>
+          <t>9578588.24935994</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>50.83</t>
+          <t>8674733.86270657</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>52.22</t>
+          <t>7392854.02435677</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>52.55</t>
+          <t>7373163.54057077</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>52.55</t>
+          <t>6926689.94202266</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>52.54</t>
+          <t>6230781.92848946</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>6102367.80961405</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>5879731.39655699</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>55.08</t>
+          <t>6167586.66505664</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>56.13</t>
+          <t>6083082.214734</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>5546984.24452394</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>5064170.97330397</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>4682675.52860823</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>59.39</t>
+          <t>4790559.66195619</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>59.39</t>
+          <t>5805036.94533039</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>395687.122769995</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>414253.625229296</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>423943.093874988</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21.57</t>
+          <t>429779.232109208</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>456637.756155731</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>471680.824199663</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>463596.227084851</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>20.31</t>
+          <t>475351.593983945</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>524065.279839791</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>601389.812449038</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>667672.730527741</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>696204.352158228</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>787031.621742149</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>926279.896561224</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>841013.388337989</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>603201.575486566</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>635044.512454601</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>36.32</t>
+          <t>637132.692268092</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>36.48</t>
+          <t>666934.611982756</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>36.31</t>
+          <t>716952.376449628</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>36.57</t>
+          <t>753803.205349431</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>751181.303721975</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>757360.84485949</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>35.98</t>
+          <t>824673.099342206</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>35.71</t>
+          <t>949221.452226363</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>35.53</t>
+          <t>1060313.74320119</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>1102337.04437576</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>1228722.9212872</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>1432613.63749969</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>1279410.61069487</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>3.94660515907954</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>4.20813902887508</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>44.92</t>
+          <t>4.39895434200082</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>4.05576652027345</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>44.63</t>
+          <t>3.84393745401302</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>44.58</t>
+          <t>3.71837242660241</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>3.27768624576948</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>46.18</t>
+          <t>3.30536135820461</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>46.88</t>
+          <t>3.38150449833357</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>47.87</t>
+          <t>3.52314959161206</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>3.5812670983585</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>3.75287972011037</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>3.90002685844947</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>4.04913386802377</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>4.0866807259061</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>76247.8401745717</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>88208.677267923</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>105366.54201057</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>116903.423250568</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19.07</t>
+          <t>127825.26007938</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>145785.517408533</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>17.91</t>
+          <t>149723.19221145</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>141915.765422544</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>17.14</t>
+          <t>131634.291310728</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>139101.288198527</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>151623.754821279</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>162996.298566998</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>171964.046082496</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>185388.454974458</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>166532.865973396</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6.35849179152629</t>
+          <t>1039.30550339848</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.59647510320646</t>
+          <t>991.497401858362</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7.91577600833963</t>
+          <t>966.696951149704</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>9.08265203935181</t>
+          <t>1018.35961891493</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>9.55018640900463</t>
+          <t>1065.13531979852</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9.45268957486545</t>
+          <t>1098.44357615741</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>9.33706799371899</t>
+          <t>1227.24107960426</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.63669632390332</t>
+          <t>1225.63015167341</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>10.7805091591203</t>
+          <t>1216.71945733123</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>11.2828615564097</t>
+          <t>1202.6701416535</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>10.8932465571719</t>
+          <t>1202.8598347468</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>10.8944331590875</t>
+          <t>1138.38555265734</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>10.927767684041</t>
+          <t>1100.19720578007</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>11.0314278268707</t>
+          <t>1059.2860433136</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>13.4917259917644</t>
+          <t>1053.15239568323</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>-6584953999.7515</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>-4606357640.6458</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-6910455754.47202</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>-7985113489.70303</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>-6523624712.10002</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>-4166294938.41091</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2392316029.16071</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>88347187.3130726</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>258133983.846553</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>1471985797.67214</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>5261480272.74281</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>8063188365.58144</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>7723039017.09417</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>5329997188.4808</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1329778300.46286</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>-9184051284.62058</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>-7846794584.51546</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>-9135925174.15885</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>-11415012584.7165</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-10746620036.3218</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>-9896185133.80101</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>-7252445454.39269</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>-4120375229.01452</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>-3335585064.68503</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1852938000.85028</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>72962132.7356738</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>3486745989.66973</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>3033514862.4137</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>1564229281.48125</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>-3240621239.45917</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.393</t>
+          <t>2599097284.86907</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.549</t>
+          <t>3240436943.86966</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.808</t>
+          <t>2225469419.68683</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>3429899095.01348</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.096</t>
+          <t>4222995324.22174</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.383</t>
+          <t>5729890195.3901</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.475</t>
+          <t>4860129425.23198</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.383</t>
+          <t>4208722416.3276</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>3593719048.53158</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.315</t>
+          <t>3324923798.52242</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.474</t>
+          <t>5188518140.00713</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.639</t>
+          <t>4576442375.91171</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2.751</t>
+          <t>4689524154.68047</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.943</t>
+          <t>3765767906.99955</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.608</t>
+          <t>1910842938.99631</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>5141.03396497066</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>5163.85631564677</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>5219.15270180865</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>5148.58846690854</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.911</t>
+          <t>5159.44886916418</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.087</t>
+          <t>5182.86588191966</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.137</t>
+          <t>5249.75228646646</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>5276.78069446516</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.153</t>
+          <t>5331.06177550676</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.257</t>
+          <t>5439.85696006406</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.423</t>
+          <t>5510.62218486244</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.601</t>
+          <t>5410.60960689171</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.734</t>
+          <t>5390.99585791342</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.879</t>
+          <t>5348.47703721959</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.472</t>
+          <t>5357.04999256373</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>4666.27265339869</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>4698.256763135</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>4771.60342739789</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>4714.6629777035</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>4724.24088741281</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>4756.93462717373</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>4812.08408600532</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>4823.69841710269</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>4879.57784534831</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>4992.65476145132</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>5068.27947657754</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>4973.25927940106</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.993</t>
+          <t>4959.75845156387</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>4926.48304539167</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>4922.06596613769</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>555.76</t>
+          <t>80757.94588551</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>593.48</t>
+          <t>99275.9509511814</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>615.85</t>
+          <t>113398.038804682</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>556.71</t>
+          <t>121689.765532206</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>523.38</t>
+          <t>140102.444069592</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>506.67</t>
+          <t>170880.422870101</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>450.18</t>
+          <t>162550.5759618</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>451.72</t>
+          <t>165015.337864437</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>450.87</t>
+          <t>168192.902988508</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>466.53</t>
+          <t>191138.676998521</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>528.35</t>
+          <t>218309.883873205</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>527.9</t>
+          <t>251495.898899498</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>544.84</t>
+          <t>275760.123560591</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>566.76</t>
+          <t>284015.872331883</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>568.67</t>
+          <t>219208.289653778</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>309.14</t>
+          <t>19457581978.2975</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>325.95</t>
+          <t>20722980160.3555</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>348.51</t>
+          <t>22355174760.9044</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>324.19</t>
+          <t>24892136393.4165</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>309.71</t>
+          <t>27019111361.8716</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>300.63</t>
+          <t>29314302188.6266</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>263.53</t>
+          <t>29687961180.8629</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>265.86</t>
+          <t>29220938046.0781</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>275.4</t>
+          <t>30735931833.4148</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>291.77</t>
+          <t>34484110048.3285</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>284.35</t>
+          <t>34327882242.1704</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>311.71</t>
+          <t>35212979274.9516</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>323.95</t>
+          <t>34767511669.1</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>332.1</t>
+          <t>34920144562.5993</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>335.77</t>
+          <t>34116318649.9577</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>365.51</t>
+          <t>71714.1974746321</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>404.52</t>
+          <t>89773.4420699027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>416.99</t>
+          <t>108932.423596312</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>392.01</t>
+          <t>124555.821418871</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>370.46</t>
+          <t>140646.907083457</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>356.37</t>
+          <t>173118.359912295</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>317.24</t>
+          <t>167753.027802991</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>322.81</t>
+          <t>168269.496953201</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>338.9</t>
+          <t>170040.23279987</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>347.4</t>
+          <t>195191.51687438</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>328.61</t>
+          <t>219826.549867641</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>366.07</t>
+          <t>250118.987651503</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>386.15</t>
+          <t>277634.012391402</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>420.61</t>
+          <t>294482.507717668</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>421.7</t>
+          <t>221336.633517797</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>154583.669</t>
+          <t>10271849972.793</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>161180.832</t>
+          <t>13442052451.6177</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>167909.414</t>
+          <t>14275685695.8212</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>172344.227</t>
+          <t>17705517399.3036</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>179376.556</t>
+          <t>20653016183.8382</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>186593.304</t>
+          <t>25809597687.3381</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>192980.837</t>
+          <t>28925007330.6535</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>197569.399</t>
+          <t>30326669215.4179</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>203263.298</t>
+          <t>31541046386.1937</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>214846.205</t>
+          <t>37068709342.1863</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>221493.104</t>
+          <t>39977146812.488</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>225132.869</t>
+          <t>42952618888.054</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>228546.245</t>
+          <t>42881475593.8707</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>244818.484</t>
+          <t>42225022411.2389</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>241454.898</t>
+          <t>33234369010.6389</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>104872.503</t>
+          <t>9043.74841087794</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>109777.856</t>
+          <t>9502.50888127876</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>117171.262</t>
+          <t>4465.61520836999</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>119524.316</t>
+          <t>-2866.05588666436</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>124051.601</t>
+          <t>-544.463013865105</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>129163.727</t>
+          <t>-2237.93704219369</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>133100.797</t>
+          <t>-5202.45184119119</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>136042.574</t>
+          <t>-3254.15908876422</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>139826.245</t>
+          <t>-1847.32981136187</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>147853.249</t>
+          <t>-4052.83987585974</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>153512.753</t>
+          <t>-1516.66599443589</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>156199.955</t>
+          <t>1376.91124799482</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>158764.32</t>
+          <t>-1873.88883081144</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>170165.48</t>
+          <t>-10466.6353857852</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>167991.262</t>
+          <t>-2128.34386401961</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>138280.818</t>
+          <t>9185732005.50449</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>146026.581</t>
+          <t>7280927708.73781</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>148962.436</t>
+          <t>8079489065.08321</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>157876.083</t>
+          <t>7186618994.11288</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>164495.211</t>
+          <t>6366095178.03342</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>171969.211</t>
+          <t>3504704501.28852</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>177649.907</t>
+          <t>762953850.209347</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>176837.961</t>
+          <t>-1105731169.33979</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>179847.025</t>
+          <t>-805114552.77896</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>190861.466</t>
+          <t>-2584599293.85781</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>200438.239</t>
+          <t>-5649264570.31763</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>200216.123</t>
+          <t>-7739639613.1024</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>199076.003</t>
+          <t>-8113963924.7707</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>212477.195</t>
+          <t>-7304877848.63953</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>205295.281</t>
+          <t>881949639.318847</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>158215.01688</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>187816.69936</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>228483.95157</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>243033.61231</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.717</t>
+          <t>275435.61188</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>322402.90247</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>341835.44225</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>352433.52206</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>338411.31909</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.949</t>
+          <t>373618.60641</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>412442.80167</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.102</t>
+          <t>476086.28522</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.229</t>
+          <t>518155.48866</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.433</t>
+          <t>565055.24448</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.279</t>
+          <t>427161.99252</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>90709.211</t>
+          <t>0.0897997267798143</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>95256.379</t>
+          <t>0.0966318540783389</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>99118.436</t>
+          <t>0.0967155811027906</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>101736.902</t>
+          <t>0.0908791055010986</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>104769.475</t>
+          <t>0.0962198199514588</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>107607.103</t>
+          <t>0.102804673546876</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>109637.748</t>
+          <t>0.102956912690638</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>110990.959</t>
+          <t>0.119628707511654</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>114289.628</t>
+          <t>0.130175374817897</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>120922.406</t>
+          <t>0.144908042253977</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>126214.668</t>
+          <t>0.154184805255565</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>126450.741</t>
+          <t>0.170525907475603</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>127513.784</t>
+          <t>0.182177954333621</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>137380.623</t>
+          <t>0.186609705464275</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>134949.702</t>
+          <t>0.152857757195951</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>97455.7494096245</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.414</t>
+          <t>104490.046105522</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>129780.475950205</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>141385.448509669</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>163673.430974625</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>198534.708527231</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>220366.953413951</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>229946.714188716</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>219849.811630637</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>225131.026493785</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>250505.955256056</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>271224.470360002</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>290200.212538196</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.926</t>
+          <t>306949.737800774</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>249769.412214035</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>21200.904</t>
+          <t>108267.244522825</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>21078.135</t>
+          <t>116025.720763604</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>21702.584</t>
+          <t>143141.854759198</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>23641.186</t>
+          <t>155905.382675339</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>25609.662</t>
+          <t>180410.815992636</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>27374.636</t>
+          <t>218524.041709291</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>31115.138</t>
+          <t>243641.18572786</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>31598.41</t>
+          <t>255166.051348419</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>31912.839</t>
+          <t>243846.129181783</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>32688.118</t>
+          <t>249651.269514551</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>33508.798</t>
+          <t>276990.218493809</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>32864.277</t>
+          <t>299601.081887128</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>32400.704</t>
+          <t>320110.562064993</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>33701.915</t>
+          <t>338513.079912929</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>33025.714</t>
+          <t>275214.601481728</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>394.66</t>
+          <t>1392977.02608068</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>420.81</t>
+          <t>1548501.44712286</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>439.9</t>
+          <t>1808213.20335516</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>405.58</t>
+          <t>1933958.79146245</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>384.39</t>
+          <t>2095563.84921221</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>371.84</t>
+          <t>2383132.17813454</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>327.77</t>
+          <t>2474514.0051568</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>330.54</t>
+          <t>2382793.95028379</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>338.15</t>
+          <t>2219608.77279353</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>352.31</t>
+          <t>2314927.23322411</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>358.13</t>
+          <t>2474490.05602413</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>375.29</t>
+          <t>2639359.39218072</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>2751211.1014522</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>404.91</t>
+          <t>2943006.74161748</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>408.67</t>
+          <t>2608367.60808784</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>9.579</t>
+          <t>108267.244522825</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.675</t>
+          <t>106874.784506361</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>7.393</t>
+          <t>118567.452818771</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>7.373</t>
+          <t>125295.415578101</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>6.927</t>
+          <t>130599.909740372</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6.231</t>
+          <t>141113.350844831</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6.102</t>
+          <t>146527.761953793</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>142271.819348647</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>6.168</t>
+          <t>139492.716818029</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>6.083</t>
+          <t>138049.766174948</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>5.547</t>
+          <t>142357.266294907</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>5.064</t>
+          <t>145945.827953273</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>4.683</t>
+          <t>148452.592679115</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>4.791</t>
+          <t>149017.803584913</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>5.805</t>
+          <t>139953.268652999</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>97455.7494096245</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>96919.1604355956</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>108187.94811472</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>113903.653820014</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>118267.395534402</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>127790.437973196</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>131722.670296693</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>126693.191381702</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>124020.556249379</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>122508.609299003</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>126749.301474092</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>130166.509035441</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>132610.280548356</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>133259.078427491</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>125264.774000791</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>201336.796527175</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>237843.243146396</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>280248.932730802</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>292659.868294661</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>329460.036347364</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>390782.643000709</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>404491.51459214</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>426966.325961581</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>420572.695258217</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>474552.861525449</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>533152.522216191</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>613075.454072872</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>673174.056485007</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>734582.076207071</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>565242.088488272</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>104872503030.034</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>109777856119.901</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>117171262020.542</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>119524316351.23</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>124051600987.441</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>129163726950.125</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>133100796901.915</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>136042574153.453</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>139826245489.659</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>147853249292.128</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>153512753127.379</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>156199954798.109</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>158764319542.08</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>170165480373.708</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>167991261881.528</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>154583669300.023</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>161180831822.752</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>167909413938.736</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>172344226626.661</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>179376556030.919</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>186593304471.612</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>192980837491.476</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>197569399294.652</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>203263298446.367</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>214846205226.631</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>221493104346.6</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>225132868999.634</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>228546245074.563</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>244818484208.255</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>241454898040.491</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>90709210755.5322</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>95256378892.9291</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>99118435730.2908</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>101736902487.975</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>104769474902.16</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>107607102793.772</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>109637748384.158</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>110990959084.762</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>114289627909.878</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>120922405644.095</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>126214667540.514</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>126450741211.991</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>127513784393.29</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>137380623420.613</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>134949701539.615</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>33127869.0257056</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>34306518.3426035</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>35189306.1721399</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>36554940.9240297</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>37969392.3967439</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>39225534.7394746</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>40103380.1659265</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>40958074.5334656</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>41655918.7881667</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>43032457.7788705</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>43701833.2099097</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>45268677.2097568</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>46080116.0593819</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>49694372.6290224</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>49055599.7627067</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>20399107.2116234</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>21258890.5286284</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>22450245.9910663</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>23214967.9702403</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>24043575.9968171</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>24921294.4908936</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>25353729.0216609</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>25781358.3755998</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>26228592.2350558</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>27179620.783703</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>27857608.0844511</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>28869197.0308023</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>29449905.6809756</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>31815688.6884885</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>31358912.4825643</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>72200832997.9626</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>74795877051.8443</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>76346732485.9179</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>78831744217.3891</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>82030457245.5939</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>84949797530.0829</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>86514939453.1646</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>88013122035.8712</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>90547765814.5052</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>94579114105.3758</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>95650792682.7358</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>98012058037.8815</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>99244457230.2164</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>106428420670.098</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>104819379402.596</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>44931874086.902</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>46891212621.2412</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>49276103823.411</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>50654784208.5588</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52599156605.2384</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>54687849781.3509</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>55434331111.4983</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>56193201728.5565</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>57784358511.485</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>60451696077.9388</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>61776778710.5061</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>63475481092.2066</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>64351890264.3354</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>69062343264.5907</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>67913886561.8142</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.264232512848511</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.260649567512397</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.257777212422185</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.258718874243415</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.258198343384027</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.25746974392098</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.2548872709022</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.254020938125548</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.252218997298688</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.250427366936407</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.244327147766521</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.23850747229835</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.236927439505582</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.234167026327657</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.234167026327657</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.501790530443466</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.50831822335499</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.522194384124724</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.525544138503226</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.525459760371842</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.525374221911579</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.539308999910502</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.542902796758459</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.550798441737517</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.561289759096373</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.570412002924493</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.584321115045995</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.587261079617403</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.593873331052796</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.593873331052796</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.233976956708023</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.231032209132613</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.220028403453091</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.215736987253359</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.216341896244131</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.217156034167441</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.205803729187298</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.203076265115992</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.196982560963796</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.188282873967219</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.185260849308986</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.177171412655655</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.175811480877015</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.171959642619547</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.171959642619547</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.375109989595781</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.370016814001778</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.363162905601156</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.364837036815617</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.363071019184611</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.36570754369466</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.363457203239857</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.361462698478045</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.359835656752129</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.357057176874857</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.35534965877495</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.346988574347895</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.346988574347895</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.346988574347895</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.346988574347895</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.426320073955752</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.428647779424658</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.449167982673274</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.446070335943492</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.446251889212711</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.445772631053733</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.457460727500405</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.461838653075254</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.468779209233201</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.478726351207042</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.482980534274965</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.495711131347982</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.495711131347982</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.495711131347982</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.495711131347982</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.198569936448467</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.201335406573564</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.18766911172557</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.189092627240891</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.190677091602679</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.188519825251608</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.179082069259738</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.176698648446701</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.171385134014671</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.164216471918101</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.161669806950084</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.157300294304124</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.157300294304124</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.157300294304124</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.157300294304124</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>561614.75147</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>641444.02132</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>763693.32324</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>805555.89709</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>910804.55933</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1087167.93383</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1137189.51954</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1180233.59939</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1152549.9274</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1257430.74966</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1422523.06488</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1601425.62333</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1734376.82332</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1879176.9176</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1471761.90399</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>309604.04105</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>353868.96391</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>423390.78749</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>448565.25097</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>509870.85234</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>609306.68471</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>648132.70032</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>682132.37731</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>664418.82444</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>724204.13104</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>810142.74071</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>912676.53596</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>993284.61855</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1073095.15612</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>840456.68997</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>8857232.93535821</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8633287.03024628</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>8463621.28549785</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>8321752.37402321</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>8210150.40736468</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>8133184.42903359</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>8040102.79782262</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>7969213.26249677</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>7917998.04505042</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>7908491.90613014</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>7932875.6864521</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>8008275.66669539</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>8120463.8563418</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>8264842.96600572</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>8315151.32656432</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
